--- a/Cooper_Minners.xlsx
+++ b/Cooper_Minners.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarud\Github\SpatialAnalysis\ChileChart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarud\Github\SpatialCharts\CooperProd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BB92C9-147F-4A5A-808D-0366EDB74C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0655A45-A52D-416E-B842-62A4FA9277DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7730" yWindow="1220" windowWidth="12460" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dimensión de Activos Mineros pa" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
   <si>
     <t>Yacimiento</t>
   </si>
@@ -130,9 +130,6 @@
     <t>MH</t>
   </si>
   <si>
-    <t>ESC</t>
-  </si>
-  <si>
     <t>CHUQ</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
     <t>CENT</t>
   </si>
   <si>
-    <t>CMZ</t>
-  </si>
-  <si>
     <t>SPENCE</t>
   </si>
   <si>
@@ -154,18 +148,12 @@
     <t>CASER</t>
   </si>
   <si>
-    <t>CAND</t>
-  </si>
-  <si>
     <t>SALV</t>
   </si>
   <si>
     <t>Code</t>
   </si>
   <si>
-    <t>GABY</t>
-  </si>
-  <si>
     <t>ABRA</t>
   </si>
   <si>
@@ -184,13 +172,19 @@
     <t>TESOR</t>
   </si>
   <si>
-    <t>LB</t>
-  </si>
-  <si>
     <t>CANDEL</t>
   </si>
   <si>
     <t>Operador</t>
+  </si>
+  <si>
+    <t>ZALD</t>
+  </si>
+  <si>
+    <t>LOM_BAY</t>
+  </si>
+  <si>
+    <t>ESCOND</t>
   </si>
 </sst>
 </file>
@@ -208,6 +202,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -470,10 +465,10 @@
         <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -490,10 +485,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -559,10 +554,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -582,10 +577,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
@@ -608,7 +603,7 @@
         <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
@@ -631,7 +626,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>14</v>
@@ -651,10 +646,10 @@
         <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>14</v>
@@ -671,13 +666,13 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>18</v>
@@ -694,13 +689,13 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>18</v>
@@ -720,10 +715,10 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>20</v>
@@ -743,10 +738,10 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -766,10 +761,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>23</v>
@@ -789,10 +784,10 @@
         <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>25</v>
@@ -812,10 +807,10 @@
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>27</v>
@@ -835,10 +830,10 @@
         <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>27</v>
@@ -858,10 +853,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>14</v>
